--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_09-09-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_09-09-2025.xlsx
@@ -528,17 +528,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -639,17 +639,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
